--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1403,49 +1403,56 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133940648</v>
+        <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>98219</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219815</v>
+        <v>5964</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Eriksberg, Granstusjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584506</v>
+        <v>584450</v>
       </c>
       <c r="R8" t="n">
-        <v>6576222</v>
+        <v>6576170</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,12 +1479,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1490,61 +1507,67 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940648</t>
+          <t>https://artportalen.se/Sighting/137077615</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133940711</v>
+        <v>133940648</v>
       </c>
       <c r="B9" t="n">
-        <v>110159</v>
+        <v>98219</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220299</v>
+        <v>219815</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1553,10 +1576,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584541</v>
+        <v>584506</v>
       </c>
       <c r="R9" t="n">
-        <v>6576261</v>
+        <v>6576222</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1615,13 +1638,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940711</t>
+          <t>https://artportalen.se/Sighting/133940648</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133940733</v>
+        <v>133940711</v>
       </c>
       <c r="B10" t="n">
         <v>110159</v>
@@ -1651,7 +1674,11 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1660,10 +1687,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584501</v>
+        <v>584541</v>
       </c>
       <c r="R10" t="n">
-        <v>6576274</v>
+        <v>6576261</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1722,33 +1749,33 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940733</t>
+          <t>https://artportalen.se/Sighting/133940711</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133940875</v>
+        <v>133940733</v>
       </c>
       <c r="B11" t="n">
-        <v>106358</v>
+        <v>110159</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221157</v>
+        <v>220299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1767,10 +1794,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>584437</v>
+        <v>584501</v>
       </c>
       <c r="R11" t="n">
-        <v>6576243</v>
+        <v>6576274</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,16 +1856,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940875</t>
+          <t>https://artportalen.se/Sighting/133940733</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128540259</v>
+        <v>133940875</v>
       </c>
       <c r="B12" t="n">
-        <v>101326</v>
+        <v>106358</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,29 +1873,25 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221157</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1878,13 +1901,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>584511</v>
+        <v>584437</v>
       </c>
       <c r="R12" t="n">
-        <v>6576249</v>
+        <v>6576243</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1908,22 +1931,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,30 +1945,31 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128540259</t>
+          <t>https://artportalen.se/Sighting/133940875</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128541582</v>
+        <v>128540259</v>
       </c>
       <c r="B13" t="n">
         <v>101326</v>
@@ -1998,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>584491</v>
+        <v>584511</v>
       </c>
       <c r="R13" t="n">
-        <v>6576206</v>
+        <v>6576249</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -2033,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,16 +2083,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128541582</t>
+          <t>https://artportalen.se/Sighting/128540259</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128603128</v>
+        <v>128541582</v>
       </c>
       <c r="B14" t="n">
-        <v>101325</v>
+        <v>101326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2104,19 +2118,27 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Eriksberg, Eriksberg, Srm</t>
+          <t>Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>584466</v>
+        <v>584491</v>
       </c>
       <c r="R14" t="n">
-        <v>6576162</v>
+        <v>6576206</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,22 +2162,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2166,36 +2188,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog på blockmark</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kent Hellström</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128603128</t>
+          <t>https://artportalen.se/Sighting/128541582</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132590936</v>
+        <v>128603128</v>
       </c>
       <c r="B15" t="n">
-        <v>101403</v>
+        <v>101325</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2221,24 +2238,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Eriksberg, Srm</t>
+          <t>Eriksberg, Eriksberg, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>584517</v>
+        <v>584466</v>
       </c>
       <c r="R15" t="n">
-        <v>6576261</v>
+        <v>6576162</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2265,12 +2274,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,31 +2298,35 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog på blockmark</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anja Hynynen</t>
+          <t>Kent Hellström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132590936</t>
+          <t>https://artportalen.se/Sighting/128603128</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133940517</v>
+        <v>132590936</v>
       </c>
       <c r="B16" t="n">
         <v>101403</v>
@@ -2333,7 +2356,11 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2342,10 +2369,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>584437</v>
+        <v>584517</v>
       </c>
       <c r="R16" t="n">
-        <v>6576243</v>
+        <v>6576261</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,12 +2399,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,13 +2431,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940517</t>
+          <t>https://artportalen.se/Sighting/132590936</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133940601</v>
+        <v>133940517</v>
       </c>
       <c r="B17" t="n">
         <v>101403</v>
@@ -2449,10 +2476,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>584464</v>
+        <v>584437</v>
       </c>
       <c r="R17" t="n">
-        <v>6576227</v>
+        <v>6576243</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,16 +2538,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940601</t>
+          <t>https://artportalen.se/Sighting/133940517</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133940516</v>
+        <v>133940601</v>
       </c>
       <c r="B18" t="n">
-        <v>99472</v>
+        <v>101403</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2528,21 +2555,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222812</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2583,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>584437</v>
+        <v>584464</v>
       </c>
       <c r="R18" t="n">
-        <v>6576243</v>
+        <v>6576227</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,47 +2645,44 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133940516</t>
+          <t>https://artportalen.se/Sighting/133940601</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128542390</v>
+        <v>133940516</v>
       </c>
       <c r="B19" t="n">
-        <v>93299</v>
+        <v>99472</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6332770</v>
+        <v>222812</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2666,13 +2690,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>584426</v>
+        <v>584437</v>
       </c>
       <c r="R19" t="n">
-        <v>6576203</v>
+        <v>6576243</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2696,22 +2720,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:48</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:48</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,16 +2741,136 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Anja Hynynen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133940516</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128542390</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93299</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Eriksberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>584426</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6576203</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby-Rekarne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128542390</t>
         </is>
@@ -2762,6 +2896,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 42245-2025 artfynd.xlsx
+++ b/artfynd/A 42245-2025 artfynd.xlsx
@@ -1406,7 +1406,7 @@
         <v>137077615</v>
       </c>
       <c r="B8" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
